--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6.49</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI46"/>
+  <dimension ref="A1:AI48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5497,27 +5497,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46076.79166666666</v>
+        <v>46076.75</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46076.875</v>
+        <v>46076.79166666666</v>
       </c>
     </row>
     <row r="45">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="N45" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46076.89583333334</v>
+        <v>46076.85416666666</v>
       </c>
     </row>
     <row r="46">
@@ -5854,116 +5854,354 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Métlaoui</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ES Tunis</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3" t="n">
+        <v>46076.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>46076.89583333334</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Spanish Town Police FC</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="3" t="n">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="n">
         <v>46076.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>6.49</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6.49</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.70833333334</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>2.37</v>
+        <v>5.87</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M35" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.70833333334</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="O25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.70833333334</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI48"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>3.99</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2879,27 +2879,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46076.64583333334</v>
+        <v>46076.625</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46076.66666666666</v>
+        <v>46076.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>5.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.89</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46076.6875</v>
+        <v>46076.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>2.82</v>
+        <v>3.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46076.69791666666</v>
+        <v>46076.6875</v>
       </c>
     </row>
     <row r="36">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M36" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46076.70833333334</v>
+        <v>46076.69791666666</v>
       </c>
     </row>
     <row r="38">
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5259,27 +5259,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,80 +5296,80 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46076.71875</v>
+        <v>46076.70833333334</v>
       </c>
     </row>
     <row r="42">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5497,27 +5497,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.94</v>
+        <v>4.58</v>
       </c>
       <c r="N43" t="n">
-        <v>5.86</v>
+        <v>6.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46076.75</v>
+        <v>46076.71875</v>
       </c>
     </row>
     <row r="44">
@@ -5616,27 +5616,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46076.79166666666</v>
+        <v>46076.75</v>
       </c>
     </row>
     <row r="45">
@@ -5735,27 +5735,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46076.85416666666</v>
+        <v>46076.79166666666</v>
       </c>
     </row>
     <row r="46">
@@ -5854,27 +5854,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46076.875</v>
+        <v>46076.85416666666</v>
       </c>
     </row>
     <row r="47">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46076.89583333334</v>
+        <v>46076.875</v>
       </c>
     </row>
     <row r="48">
@@ -6097,111 +6097,230 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="n">
+        <v>46076.89583333334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="L49" t="n">
         <v>1.79</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M49" t="n">
         <v>3.54</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N49" t="n">
         <v>4.35</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AB49" t="n">
         <v>2</v>
       </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="3" t="n">
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
         <v>46076.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,27 +856,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46076.39583333334</v>
+        <v>46076.375</v>
       </c>
     </row>
     <row r="5">
@@ -975,27 +975,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46076.41666666666</v>
+        <v>46076.39583333334</v>
       </c>
     </row>
     <row r="6">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46076.4375</v>
+        <v>46076.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46076.5</v>
+        <v>46076.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>5.83</v>
+        <v>4.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46076.51041666666</v>
+        <v>46076.5</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.19</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>5.83</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46076.54166666666</v>
+        <v>46076.51041666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46076.57291666666</v>
+        <v>46076.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46076.58333333334</v>
+        <v>46076.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.84</v>
+        <v>3.31</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4.71</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46076.60416666666</v>
+        <v>46076.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>1.84</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>4.71</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46076.625</v>
+        <v>46076.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46076.64583333334</v>
+        <v>46076.625</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>3.57</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46076.66666666666</v>
+        <v>46076.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="O24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.5</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46076.6875</v>
+        <v>46076.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>2.94</v>
       </c>
       <c r="N35" t="n">
-        <v>3.89</v>
+        <v>2.22</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46076.69791666666</v>
+        <v>46076.6875</v>
       </c>
     </row>
     <row r="37">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M37" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46076.70833333334</v>
+        <v>46076.69791666666</v>
       </c>
     </row>
     <row r="39">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>5.87</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>3.15</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="N41" t="n">
-        <v>5.87</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46076.71875</v>
+        <v>46076.70833333334</v>
       </c>
     </row>
     <row r="43">
@@ -5616,27 +5616,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.48</v>
+        <v>2.13</v>
       </c>
       <c r="M44" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>5.86</v>
+        <v>3.29</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46076.75</v>
+        <v>46076.71875</v>
       </c>
     </row>
     <row r="45">
@@ -5735,27 +5735,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46076.79166666666</v>
+        <v>46076.75</v>
       </c>
     </row>
     <row r="46">
@@ -5854,27 +5854,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46076.85416666666</v>
+        <v>46076.79166666666</v>
       </c>
     </row>
     <row r="47">
@@ -5973,27 +5973,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46076.875</v>
+        <v>46076.85416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46076.89583333334</v>
+        <v>46076.875</v>
       </c>
     </row>
     <row r="49">
@@ -6216,111 +6216,230 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>46076.89583333334</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="L50" t="n">
         <v>1.79</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M50" t="n">
         <v>3.54</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N50" t="n">
         <v>4.35</v>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AB50" t="n">
         <v>2</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="3" t="n">
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
         <v>46076.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>5.87</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>6.81</v>
+        <v>3.29</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
       <c r="N44" t="n">
-        <v>3.29</v>
+        <v>6.81</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>6.49</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>4.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.47</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N29" t="n">
         <v>4.6</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>3.15</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>5.87</v>
+        <v>2.37</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,77 +5415,77 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>5.87</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="N22" t="n">
-        <v>4.57</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7.49</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>1.47</v>
+        <v>3.89</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>7.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>3.89</v>
+        <v>1.47</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M38" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
       <c r="N43" t="n">
-        <v>3.29</v>
+        <v>6.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M44" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>6.81</v>
+        <v>3.29</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.25</v>
+        <v>7.49</v>
       </c>
       <c r="M32" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="N34" t="n">
-        <v>5.83</v>
+        <v>2.22</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>7.49</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>1.47</v>
+        <v>5.83</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,77 +5415,77 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>6.81</v>
+        <v>3.29</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
       <c r="N44" t="n">
-        <v>3.29</v>
+        <v>6.81</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="193">
   <si>
     <t>Date</t>
   </si>
@@ -184,9 +184,6 @@
     <t>20:30</t>
   </si>
   <si>
-    <t>21:00</t>
-  </si>
-  <si>
     <t>21:30</t>
   </si>
   <si>
@@ -199,21 +196,21 @@
     <t>Singapore S.League</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>FYR Macedonia First Football League</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Iran Persian Gulf Pro League</t>
   </si>
   <si>
@@ -244,24 +241,24 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Saudi Arabia Professional League</t>
+  </si>
+  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
-    <t>Saudi Arabia Professional League</t>
-  </si>
-  <si>
     <t>Netherlands Eerste Divisie</t>
   </si>
   <si>
+    <t>Italy Serie C Group A</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Italy Serie C Group A</t>
-  </si>
-  <si>
     <t>Italy Serie C Group B</t>
   </si>
   <si>
@@ -280,21 +277,18 @@
     <t>England EFL League Two</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
@@ -319,24 +313,24 @@
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
     <t>Pendikspor</t>
   </si>
   <si>
     <t>Makedonija GjP</t>
   </si>
   <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
     <t>PSIM Yogyakarta</t>
   </si>
   <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
     <t>Sepahan</t>
   </si>
   <si>
@@ -346,24 +340,24 @@
     <t>Videoton</t>
   </si>
   <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
     <t>Amed</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
     <t>Fiorentina</t>
   </si>
   <si>
+    <t>FCSB</t>
+  </si>
+  <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
-    <t>FCSB</t>
-  </si>
-  <si>
     <t>Trakai</t>
   </si>
   <si>
@@ -373,45 +367,45 @@
     <t>Maccabi Netanya</t>
   </si>
   <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
+    <t>Al Fateh</t>
+  </si>
+  <si>
     <t>MTK</t>
   </si>
   <si>
-    <t>Dhamk</t>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>AZ II</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Emmen</t>
+    <t>Virtus Verona</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Ternana</t>
+  </si>
+  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Virtus Verona</t>
-  </si>
-  <si>
-    <t>Ternana</t>
-  </si>
-  <si>
     <t>Le Mans</t>
   </si>
   <si>
@@ -430,12 +424,12 @@
     <t>Walsall</t>
   </si>
   <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
     <t>Cobreloa</t>
   </si>
   <si>
@@ -445,9 +439,6 @@
     <t>Curicó Unido</t>
   </si>
   <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
     <t>Libertad</t>
   </si>
   <si>
@@ -466,24 +457,24 @@
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
     <t>Keçiörengücü</t>
   </si>
   <si>
     <t>Tikveš</t>
   </si>
   <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
     <t>Esteghlal Khuzestan</t>
   </si>
   <si>
@@ -493,24 +484,24 @@
     <t>Kecskeméti TE</t>
   </si>
   <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
     <t>Van BB</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
     <t>Pisa</t>
   </si>
   <si>
+    <t>Metaloglobus</t>
+  </si>
+  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Metaloglobus</t>
-  </si>
-  <si>
     <t>Kauno Žalgiris</t>
   </si>
   <si>
@@ -520,45 +511,45 @@
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Al Akhdoud</t>
+  </si>
+  <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Al Ahli</t>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>Al Ittifaq</t>
+  </si>
+  <si>
+    <t>Al Riyadh</t>
   </si>
   <si>
     <t>Den Bosch</t>
   </si>
   <si>
-    <t>Al Riyadh</t>
-  </si>
-  <si>
-    <t>Al Akhdoud</t>
-  </si>
-  <si>
-    <t>Al Ittifaq</t>
-  </si>
-  <si>
-    <t>Ajax II</t>
+    <t>Vicenza</t>
   </si>
   <si>
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Real Sociedad II</t>
+  </si>
+  <si>
+    <t>Forlì</t>
+  </si>
+  <si>
     <t>El Geish</t>
   </si>
   <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Real Sociedad II</t>
-  </si>
-  <si>
-    <t>Vicenza</t>
-  </si>
-  <si>
-    <t>Forlì</t>
-  </si>
-  <si>
     <t>Guingamp</t>
   </si>
   <si>
@@ -577,12 +568,12 @@
     <t>Milton Keynes Dons</t>
   </si>
   <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
     <t>Paços de Ferreira</t>
   </si>
   <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
@@ -590,9 +581,6 @@
   </si>
   <si>
     <t>Magallanes</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
   </si>
   <si>
     <t>Manta FC</t>
@@ -968,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI50"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1086,16 +1074,16 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1110,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1193,16 +1181,16 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1217,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1300,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1324,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1407,16 +1395,16 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1431,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1514,16 +1502,16 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1538,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1621,16 +1609,16 @@
         <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1645,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1728,16 +1716,16 @@
         <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1752,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1835,16 +1823,16 @@
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1859,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1942,16 +1930,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1966,16 +1954,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L10">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="M10">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N10">
-        <v>2.65</v>
+        <v>4.47</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2049,16 +2037,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2073,16 +2061,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L11">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="M11">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N11">
-        <v>4.47</v>
+        <v>2.65</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2156,16 +2144,16 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2180,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L12">
         <v>1.58</v>
@@ -2263,16 +2251,16 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2287,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L13">
         <v>6.19</v>
@@ -2370,16 +2358,16 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2394,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L14">
         <v>2.7</v>
@@ -2477,16 +2465,16 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2501,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2587,13 +2575,13 @@
         <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2608,16 +2596,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L16">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2691,16 +2679,16 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F17" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2715,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2798,16 +2786,16 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2822,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L18">
         <v>1.84</v>
@@ -2905,16 +2893,16 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2929,16 +2917,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L19">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="M19">
-        <v>3.74</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>3.99</v>
+        <v>17</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3012,16 +3000,16 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3036,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L20">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="M20">
-        <v>7</v>
+        <v>3.74</v>
       </c>
       <c r="N20">
-        <v>17</v>
+        <v>3.99</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3119,16 +3107,16 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3143,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3226,16 +3214,16 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3250,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L22">
         <v>1.66</v>
@@ -3333,16 +3321,16 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3357,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L23">
         <v>3.57</v>
@@ -3440,16 +3428,16 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3464,16 +3452,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L24">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -3547,16 +3535,16 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3571,16 +3559,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L25">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -3654,16 +3642,16 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3678,16 +3666,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -3764,13 +3752,13 @@
         <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3785,76 +3773,76 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L27">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="M27">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N27">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI27" s="3">
         <v>46076.66666666666</v>
@@ -3868,16 +3856,16 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3892,16 +3880,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -3975,16 +3963,16 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3999,16 +3987,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L29">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M29">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N29">
-        <v>6.49</v>
+        <v>4.6</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4082,16 +4070,16 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F30" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4106,76 +4094,76 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="L30">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3">
         <v>46076.66666666666</v>
@@ -4189,16 +4177,16 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4213,16 +4201,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4261,10 +4249,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -4299,13 +4287,13 @@
         <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4320,16 +4308,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L32">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4403,16 +4391,16 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4427,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4510,16 +4498,16 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4534,16 +4522,16 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L34">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M34">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="N34">
-        <v>3.89</v>
+        <v>5.83</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4617,16 +4605,16 @@
         <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4641,16 +4629,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L35">
-        <v>7.49</v>
+        <v>3.25</v>
       </c>
       <c r="M35">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="N35">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -4689,10 +4677,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -4724,16 +4712,16 @@
         <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F36" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4748,16 +4736,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L36">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -4831,16 +4819,16 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F37" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4855,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L37">
         <v>2.44</v>
@@ -4938,16 +4926,16 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4962,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L38">
         <v>1.93</v>
@@ -5045,16 +5033,16 @@
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F39" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5069,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -5152,16 +5140,16 @@
         <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5176,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L40">
         <v>1.56</v>
@@ -5259,16 +5247,16 @@
         <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5283,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L41">
         <v>3.15</v>
@@ -5366,16 +5354,16 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F42" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5390,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L42">
         <v>2.48</v>
@@ -5473,16 +5461,16 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F43" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -5497,16 +5485,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L43">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M43">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
       <c r="N43">
-        <v>3.29</v>
+        <v>6.81</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5545,10 +5533,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -5580,16 +5568,16 @@
         <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5604,16 +5592,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L44">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M44">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="N44">
-        <v>6.81</v>
+        <v>3.29</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -5652,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -5687,16 +5675,16 @@
         <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E45" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F45" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5711,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L45">
         <v>1.48</v>
@@ -5794,16 +5782,16 @@
         <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F46" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5818,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5901,31 +5889,31 @@
         <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F47" t="s">
+        <v>188</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
         <v>191</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="s">
-        <v>195</v>
       </c>
       <c r="L47">
         <v>2.12</v>
@@ -6008,16 +5996,16 @@
         <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
         <v>94</v>
       </c>
       <c r="E48" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6032,16 +6020,16 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6080,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -6104,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3">
-        <v>46076.875</v>
+        <v>46076.89583333334</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -6112,19 +6100,19 @@
         <v>46076</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E49" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F49" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -6139,16 +6127,16 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L49">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -6187,10 +6175,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -6211,113 +6199,6 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3">
-        <v>46076.89583333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:35">
-      <c r="A50" s="2">
-        <v>46076</v>
-      </c>
-      <c r="B50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D50" t="s">
-        <v>94</v>
-      </c>
-      <c r="E50" t="s">
-        <v>145</v>
-      </c>
-      <c r="F50" t="s">
-        <v>194</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50" t="s">
-        <v>195</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50">
-        <v>0</v>
-      </c>
-      <c r="AI50" s="3">
         <v>46076.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1501,64 +1501,64 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46076.4375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.4</v>
       </c>
-      <c r="N10" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46076.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>4.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2096,40 +2096,40 @@
         <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
         <v>2</v>
@@ -2138,22 +2138,22 @@
         <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46076.57291666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>3.74</v>
       </c>
       <c r="N21" t="n">
-        <v>17</v>
+        <v>3.99</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="M34" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.22</v>
+        <v>5.83</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>5.87</v>
+        <v>2.65</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>5.87</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
       <c r="N43" t="n">
-        <v>3.29</v>
+        <v>6.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M44" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>6.81</v>
+        <v>3.29</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.47</v>
+        <v>4.14</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1977,40 +1977,40 @@
         <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
         <v>1.95</v>
@@ -2019,22 +2019,22 @@
         <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46076.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.31</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>9.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="N18" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
         <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.60416666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>3.74</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>3.99</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>6.49</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.8</v>
       </c>
-      <c r="N27" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.46</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z30" t="n">
         <v>5</v>
       </c>
-      <c r="O30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="AA30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.18</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.49</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>7.49</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.47</v>
+        <v>5.83</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.25</v>
+        <v>7.49</v>
       </c>
       <c r="M36" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M38" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>5.87</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>5.87</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.25</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH16" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.92</v>
+        <v>9.5</v>
       </c>
       <c r="O17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.6</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q22" t="n">
+        <v>13</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V22" t="n">
         <v>3.8</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>5.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>4.72</v>
+        <v>2.61</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="N26" t="n">
-        <v>6.49</v>
+        <v>4.72</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.25</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>7.49</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>5.83</v>
+        <v>1.47</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M37" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N38" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>5.87</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.6</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46076.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.14</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.6</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.92</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.5</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>9.5</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.7</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V21" t="n">
         <v>3.8</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>5.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.72</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.5</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>2.73</v>
       </c>
       <c r="O28" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.05</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="AD28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="O29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>7.49</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>3.89</v>
+        <v>1.47</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>2.94</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>2.22</v>
+        <v>3.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M38" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>3.15</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="N41" t="n">
-        <v>5.87</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4.14</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.6</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46076.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.6</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AF11" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.25</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH16" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.92</v>
+        <v>9.5</v>
       </c>
       <c r="O17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.6</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>3.99</v>
       </c>
       <c r="O19" t="n">
         <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.4</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>13</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AE21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.8</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>5.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="N23" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.64583333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.05</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AD26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
-        <v>3.78</v>
+        <v>4.75</v>
       </c>
       <c r="N28" t="n">
-        <v>2.73</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>5.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="V28" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="W28" t="n">
         <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>2.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.5</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7.49</v>
+        <v>2.87</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="N31" t="n">
-        <v>1.47</v>
+        <v>2.62</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>3.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.22</v>
+        <v>5.83</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>7.49</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>3.89</v>
+        <v>1.47</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>4.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>5.83</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>5.87</v>
+        <v>2.65</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.15</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>3.64</v>
+        <v>3.94</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>5.66</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>6.81</v>
+        <v>3.29</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.29</v>
+        <v>5.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5779,70 +5779,70 @@
         <v>1.48</v>
       </c>
       <c r="M45" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="N45" t="n">
-        <v>5.86</v>
+        <v>5.8</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF45" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AG45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH45" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.75</v>
@@ -6023,40 +6023,40 @@
         <v>3.1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA47" t="n">
         <v>2.1</v>
@@ -6065,22 +6065,22 @@
         <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46076.85416666666</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P2" t="n">
         <v>2.3</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
         <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1522,13 +1522,13 @@
         <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.33</v>
@@ -1540,22 +1540,22 @@
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
         <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
         <v>1.62</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.25</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46076.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.14</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.6</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.19</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
         <v>2.1</v>
@@ -1992,7 +1992,7 @@
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
         <v>1.4</v>
@@ -2004,7 +2004,7 @@
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
@@ -2013,13 +2013,13 @@
         <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
         <v>1.29</v>
@@ -2096,19 +2096,19 @@
         <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
         <v>2.9</v>
@@ -2117,28 +2117,28 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
         <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
         <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
         <v>1.29</v>
@@ -2150,10 +2150,10 @@
         <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46076.57291666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.92</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>2.15</v>
@@ -2581,49 +2581,49 @@
         <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>6.35</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
         <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD18" t="n">
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>4.57</v>
+        <v>17</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V21" t="n">
         <v>3.8</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>5.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.72</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.73</v>
+        <v>6.49</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6.49</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.75</v>
+        <v>3.78</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="O28" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.04</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="V28" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="W28" t="n">
         <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.05</v>
+        <v>5.04</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>4.75</v>
+        <v>3.98</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.18</v>
+        <v>2.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>1.66</v>
       </c>
       <c r="M30" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="O31" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="T31" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.15</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AE31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="M32" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>11</v>
+        <v>7.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.85</v>
+        <v>3.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.49</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="N34" t="n">
-        <v>1.47</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.03</v>
+        <v>3.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>7.49</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>3.89</v>
+        <v>1.47</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4705,28 +4705,28 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.8</v>
+        <v>5.29</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O36" t="n">
         <v>5.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R36" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
         <v>3.2</v>
@@ -4741,7 +4741,7 @@
         <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y36" t="n">
         <v>1.38</v>
@@ -4750,13 +4750,13 @@
         <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AD36" t="n">
         <v>1.22</v>
@@ -4768,10 +4768,10 @@
         <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>2.01</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M37" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>2.82</v>
+        <v>4.33</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.48</v>
+        <v>1.58</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>5.66</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="M41" t="n">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>5.66</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P41" t="n">
         <v>2</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q41" t="n">
-        <v>6.45</v>
+        <v>3.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
         <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="N43" t="n">
-        <v>3.29</v>
+        <v>5.25</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.71875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.25</v>
+        <v>3.36</v>
       </c>
       <c r="O44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P44" t="n">
         <v>2.1</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V44" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD44" t="n">
         <v>1.25</v>
       </c>
       <c r="AE44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF44" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF44" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1730,43 +1730,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
         <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
         <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
         <v>1.36</v>
@@ -1775,7 +1775,7 @@
         <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
         <v>1.67</v>
@@ -1784,7 +1784,7 @@
         <v>3.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
         <v>1.85</v>
@@ -1793,10 +1793,10 @@
         <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.29</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
@@ -2230,49 +2230,49 @@
         <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.23</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.2</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>11.5</v>
       </c>
       <c r="O16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.6</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.08</v>
-      </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.5</v>
       </c>
-      <c r="V16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH17" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="O19" t="n">
         <v>2.3</v>
@@ -2703,7 +2703,7 @@
         <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
         <v>2.5</v>
@@ -2718,22 +2718,22 @@
         <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
         <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB19" t="n">
         <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AD19" t="n">
         <v>1.33</v>
@@ -2742,7 +2742,7 @@
         <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
         <v>2.73</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P28" t="n">
         <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
         <v>1.22</v>
@@ -3780,7 +3780,7 @@
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
         <v>4.33</v>
@@ -3792,10 +3792,10 @@
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
         <v>1.42</v>
@@ -3807,16 +3807,16 @@
         <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF28" t="n">
         <v>2.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
         <v>1.6</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>4.16</v>
       </c>
       <c r="N30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V30" t="n">
         <v>4.6</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>7.49</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="O31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AC31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>5.83</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>5.83</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>5.29</v>
       </c>
       <c r="M34" t="n">
-        <v>2.45</v>
+        <v>3.39</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>1.64</v>
       </c>
       <c r="O34" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P34" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T34" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE34" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AF34" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.53</v>
+        <v>2.01</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>7.49</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="N35" t="n">
-        <v>1.47</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.03</v>
+        <v>3.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,61 +4705,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE36" t="n">
         <v>2.1</v>
@@ -4768,10 +4768,10 @@
         <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.01</v>
+        <v>1.42</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>4.33</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.33</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
         <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>5.66</v>
+        <v>1.94</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="P39" t="n">
         <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.45</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.95</v>
+        <v>1.58</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>5.66</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.06</v>
+        <v>6.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U40" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V40" t="n">
         <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
         <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC40" t="n">
         <v>3</v>
       </c>
-      <c r="AA40" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF40" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF40" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T41" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U41" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X41" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>5.25</v>
+        <v>3.36</v>
       </c>
       <c r="O43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P43" t="n">
         <v>2.1</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD43" t="n">
         <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.71875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="M44" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z44" t="n">
         <v>3.2</v>
       </c>
-      <c r="N44" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V44" t="n">
-        <v>7</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3</v>
-      </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="AD44" t="n">
         <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -680,10 +680,10 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
         <v>1.44</v>
@@ -698,22 +698,22 @@
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
         <v>2.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
         <v>1.75</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.44</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46076.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
         <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.8</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8</v>
+        <v>6.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.27</v>
+        <v>2.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>6.15</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>2.27</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="M25" t="n">
         <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>2.73</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V26" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="O27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>4.16</v>
       </c>
       <c r="N28" t="n">
-        <v>2.73</v>
+        <v>1.56</v>
       </c>
       <c r="O28" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.22</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W28" t="n">
+      <c r="AH28" t="n">
         <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N30" t="n">
         <v>4.6</v>
       </c>
-      <c r="M30" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.56</v>
-      </c>
       <c r="O30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7.49</v>
+        <v>1.91</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>2.97</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="N32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V32" t="n">
+        <v>12</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC32" t="n">
         <v>5.83</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.91</v>
+        <v>5.29</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>1.64</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE33" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>2.01</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,61 +4467,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="N34" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S34" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V34" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
         <v>1.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE34" t="n">
         <v>2.1</v>
@@ -4530,10 +4530,10 @@
         <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.01</v>
+        <v>1.42</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>5.83</v>
       </c>
       <c r="O35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.5</v>
+        <v>7.49</v>
       </c>
       <c r="M36" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="O36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="N39" t="n">
-        <v>1.94</v>
+        <v>5.66</v>
       </c>
       <c r="O39" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
         <v>2.25</v>
       </c>
       <c r="Q39" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH39" t="n">
         <v>2.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.58</v>
+        <v>2.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>5.66</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P40" t="n">
         <v>2</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q40" t="n">
-        <v>6.45</v>
+        <v>3.06</v>
       </c>
       <c r="R40" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="T40" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U40" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V40" t="n">
         <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
         <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF40" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1522,13 +1522,13 @@
         <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.33</v>
@@ -1537,13 +1537,13 @@
         <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB9" t="n">
         <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
         <v>1.25</v>
@@ -1555,10 +1555,10 @@
         <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46076.4375</v>
@@ -1611,40 +1611,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
         <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.06</v>
@@ -1656,7 +1656,7 @@
         <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
         <v>1.67</v>
@@ -1668,10 +1668,10 @@
         <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
         <v>1.33</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>6.15</v>
+        <v>4.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.74</v>
+        <v>2.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>4.8</v>
+        <v>6.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.27</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.77</v>
+        <v>1.19</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="N20" t="n">
-        <v>4.25</v>
+        <v>17</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="V20" t="n">
-        <v>5.75</v>
+        <v>3.88</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.2</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.3</v>
+        <v>3.94</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3161,7 +3161,7 @@
         <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
         <v>1.87</v>
@@ -3170,7 +3170,7 @@
         <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q23" t="n">
         <v>2.38</v>
@@ -3188,25 +3188,25 @@
         <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
         <v>2.2</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>2.28</v>
       </c>
       <c r="M26" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.04</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="W26" t="n">
         <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.5</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.16</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>1.56</v>
+        <v>6.49</v>
       </c>
       <c r="O28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>5.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.97</v>
+        <v>3.52</v>
       </c>
       <c r="M32" t="n">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="T32" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="U32" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="V32" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.08</v>
+        <v>2.49</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.83</v>
+        <v>4.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.29</v>
+        <v>2.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.39</v>
+        <v>2.45</v>
       </c>
       <c r="N33" t="n">
-        <v>1.64</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="P33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V33" t="n">
+        <v>15</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.5</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG33" t="n">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,61 +4467,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.5</v>
+        <v>5.29</v>
       </c>
       <c r="M34" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="O34" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
         <v>1.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
         <v>2.1</v>
@@ -4530,10 +4530,10 @@
         <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>5.83</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="U40" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N41" t="n">
         <v>3.5</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
         <v>3.7</v>
       </c>
-      <c r="N41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S41" t="n">
         <v>2.4</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="U41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V41" t="n">
+        <v>10</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.5</v>
       </c>
-      <c r="V41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AC41" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T42" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U42" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE42" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5776,22 +5776,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
         <v>5.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>5.92</v>
       </c>
       <c r="R45" t="n">
         <v>1.42</v>
@@ -5800,10 +5800,10 @@
         <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V45" t="n">
         <v>7.5</v>
@@ -5812,19 +5812,19 @@
         <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
         <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
         <v>3.8</v>
@@ -6020,46 +6020,46 @@
         <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
         <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S47" t="n">
         <v>2.66</v>
       </c>
       <c r="T47" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U47" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
         <v>1.7</v>
@@ -6068,7 +6068,7 @@
         <v>3.58</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE47" t="n">
         <v>1.82</v>
@@ -6077,7 +6077,7 @@
         <v>1.87</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
         <v>1.62</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1260,10 +1260,10 @@
         <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P7" t="n">
         <v>2.25</v>
@@ -1275,37 +1275,37 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
         <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>5.95</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AH10" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46076.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="M11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.1</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.45</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
         <v>2.1</v>
@@ -1992,37 +1992,37 @@
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
         <v>1.83</v>
@@ -2031,10 +2031,10 @@
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46076.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>6.55</v>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.29</v>
+        <v>1.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.59</v>
+        <v>7.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>3.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.22</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="Z16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.25</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH16" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>1.93</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>2.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2807,64 +2807,64 @@
         <v>7.5</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="T20" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC20" t="n">
         <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AH20" t="n">
         <v>6</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.7</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.94</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>4.16</v>
       </c>
       <c r="N24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="N26" t="n">
-        <v>2.73</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.8</v>
       </c>
-      <c r="N28" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.46</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>2.97</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="N31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V31" t="n">
+        <v>15</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC31" t="n">
         <v>5.83</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.52</v>
+        <v>5.29</v>
       </c>
       <c r="M32" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="O32" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="R32" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.04</v>
@@ -4268,34 +4268,34 @@
         <v>1.07</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.97</v>
+        <v>5.6</v>
       </c>
       <c r="M33" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>1.55</v>
       </c>
       <c r="O33" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="R33" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>15</v>
+        <v>7.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC33" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AE33" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.29</v>
+        <v>1.91</v>
       </c>
       <c r="M34" t="n">
         <v>3.4</v>
       </c>
       <c r="N34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.67</v>
       </c>
-      <c r="O34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC34" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P35" t="n">
         <v>1.91</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S35" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="V35" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>7.49</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>1.47</v>
+        <v>5.09</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>4.33</v>
+        <v>2.94</v>
       </c>
       <c r="O37" t="n">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
         <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>4.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="P38" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.58</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>5.66</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P39" t="n">
         <v>2</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q39" t="n">
-        <v>6.45</v>
+        <v>3.06</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
         <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
         <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA39" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG39" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.5</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.7</v>
       </c>
-      <c r="N40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S40" t="n">
         <v>2.4</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T40" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="U40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V40" t="n">
+        <v>10</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.5</v>
       </c>
-      <c r="V40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AC40" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="N41" t="n">
-        <v>3.5</v>
+        <v>5.66</v>
       </c>
       <c r="O41" t="n">
-        <v>3.12</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.7</v>
+        <v>6.45</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
         <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z43" t="n">
         <v>3.2</v>
       </c>
-      <c r="N43" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V43" t="n">
-        <v>7</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3</v>
-      </c>
       <c r="AA43" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE43" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.71875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P44" t="n">
         <v>2.1</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V44" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
         <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AD44" t="n">
         <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
@@ -802,13 +802,13 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.1</v>
@@ -817,34 +817,34 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
         <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1507,10 +1507,10 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
         <v>2.62</v>
@@ -1522,40 +1522,40 @@
         <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
         <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
         <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
         <v>1.57</v>
@@ -1620,7 +1620,7 @@
         <v>3.85</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
@@ -1632,7 +1632,7 @@
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="T10" t="n">
         <v>3.25</v>
@@ -1641,25 +1641,25 @@
         <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>3.55</v>
@@ -1668,10 +1668,10 @@
         <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
         <v>1.36</v>
@@ -2102,13 +2102,13 @@
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
         <v>2.9</v>
@@ -2117,7 +2117,7 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>1.07</v>
@@ -2129,10 +2129,10 @@
         <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
         <v>1.73</v>
@@ -2141,7 +2141,7 @@
         <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
         <v>1.75</v>
@@ -2150,7 +2150,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
         <v>1.4</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>6.55</v>
+        <v>4.04</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.7</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="AB15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.25</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH15" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,40 +2325,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>3.29</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.25</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
@@ -2370,28 +2370,28 @@
         <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.93</v>
+        <v>9.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.59</v>
+        <v>8.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.11</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>5.36</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -2587,10 +2587,10 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
         <v>5.8</v>
@@ -2599,34 +2599,34 @@
         <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AD18" t="n">
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
         <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
         <v>2.1</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>16</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.91</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH21" t="n">
         <v>6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,37 +3039,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
         <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.1</v>
@@ -3078,34 +3078,34 @@
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="AA22" t="n">
         <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N24" t="n">
         <v>4.6</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.56</v>
-      </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="N25" t="n">
-        <v>6.49</v>
+        <v>1.55</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>1.34</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3759,58 +3759,58 @@
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
         <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
         <v>2.8</v>
@@ -3819,7 +3819,7 @@
         <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>1.29</v>
       </c>
       <c r="M30" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>6.49</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="O31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R31" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="T31" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.15</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AE31" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4238,10 +4238,10 @@
         <v>1.67</v>
       </c>
       <c r="O32" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>2.38</v>
@@ -4259,37 +4259,37 @@
         <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
         <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
         <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.6</v>
+        <v>2.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="N33" t="n">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V33" t="n">
+        <v>12</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="AA33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V33" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1.91</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF34" t="n">
         <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.52</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.9</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>4.15</v>
       </c>
       <c r="O37" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="P37" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,31 +4943,31 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="O38" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
         <v>1.33</v>
@@ -4976,40 +4976,40 @@
         <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="AD38" t="n">
         <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="M39" t="n">
         <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="O39" t="n">
         <v>3.4</v>
@@ -5080,13 +5080,13 @@
         <v>3.06</v>
       </c>
       <c r="R39" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T39" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="U39" t="n">
         <v>1.33</v>
@@ -5098,28 +5098,28 @@
         <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA39" t="n">
         <v>2.13</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF39" t="n">
         <v>1.91</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.7</v>
+        <v>2.53</v>
       </c>
       <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U40" t="n">
         <v>1.5</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.29</v>
       </c>
-      <c r="V40" t="n">
-        <v>10</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.5</v>
+        <v>2.18</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="N42" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="R42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.3</v>
       </c>
-      <c r="S42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V42" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.23</v>
+        <v>1.56</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="AD42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.43</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="O43" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.74</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T43" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
         <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.71875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>5.65</v>
       </c>
       <c r="O44" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="P44" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="R44" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T44" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U44" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V44" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W44" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
         <v>1.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>4.04</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.29</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
         <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.29</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
         <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.625</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.19</v>
+        <v>1.99</v>
       </c>
       <c r="M21" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>3.66</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>13</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.15</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.22</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z21" t="n">
-        <v>6.25</v>
+        <v>4.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>2.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,37 +3039,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
         <v>1.1</v>
@@ -3078,34 +3078,34 @@
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.35</v>
+        <v>3.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>4.16</v>
+        <v>4.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>4.82</v>
+        <v>1.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>5.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>2.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4.6</v>
+        <v>4.16</v>
       </c>
       <c r="N26" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>1.34</v>
       </c>
       <c r="O27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.2</v>
+        <v>5.09</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.03</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.6875</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.29</v>
+        <v>1.91</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.67</v>
       </c>
-      <c r="O32" t="n">
-        <v>5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>9</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="M33" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S33" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AC33" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.6</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="N34" t="n">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>12</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="AA34" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>5.29</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="O35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.7</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>5.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>5.09</v>
+        <v>1.55</v>
       </c>
       <c r="O36" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>2.11</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V36" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.33</v>
       </c>
-      <c r="V36" t="n">
-        <v>8</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z36" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>4.15</v>
+        <v>2.83</v>
       </c>
       <c r="O37" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
         <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="AD37" t="n">
         <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="N38" t="n">
-        <v>2.83</v>
+        <v>4.15</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="AD38" t="n">
         <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.9</v>
+        <v>1.58</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="N39" t="n">
-        <v>2.39</v>
+        <v>5.66</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.06</v>
+        <v>6.45</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
         <v>7.6</v>
       </c>
       <c r="W39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X39" t="n">
         <v>1.05</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y39" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AD39" t="n">
         <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
       <c r="M41" t="n">
-        <v>3.94</v>
+        <v>2.96</v>
       </c>
       <c r="N41" t="n">
-        <v>5.66</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P41" t="n">
         <v>2</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q41" t="n">
-        <v>6.45</v>
+        <v>4.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AC41" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
         <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="T42" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X42" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE42" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="N43" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z43" t="n">
         <v>3.25</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V43" t="n">
-        <v>7</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.71875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="M44" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.65</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V44" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.22</v>
+        <v>1.73</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5776,22 +5776,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="N45" t="n">
         <v>5.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.92</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
         <v>1.42</v>
@@ -5821,10 +5821,10 @@
         <v>3</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>3.8</v>
@@ -5833,7 +5833,7 @@
         <v>1.22</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
         <v>1.75</v>
@@ -6020,22 +6020,22 @@
         <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="R47" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T47" t="n">
         <v>2.8</v>
@@ -6050,13 +6050,13 @@
         <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA47" t="n">
         <v>2</v>
@@ -6065,16 +6065,16 @@
         <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="AD47" t="n">
         <v>1.21</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
         <v>1.33</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46076.5</v>
+        <v>46076.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.41</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.58</v>
+        <v>2.57</v>
       </c>
       <c r="M12" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.83</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46076.51041666666</v>
+        <v>46076.5</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>5.83</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46076.54166666666</v>
+        <v>46076.51041666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.7</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46076.57291666666</v>
+        <v>46076.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.29</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46076.58333333334</v>
+        <v>46076.57291666666</v>
       </c>
     </row>
     <row r="16">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>4.04</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>3.29</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
         <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>6.3</v>
+        <v>4.04</v>
       </c>
       <c r="N17" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.82</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.31</v>
+        <v>2.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="N18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z18" t="n">
         <v>5</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.11</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46076.60416666666</v>
+        <v>46076.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,27 +2641,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46076.625</v>
+        <v>46076.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.87</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.38</v>
+        <v>13</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="S23" t="n">
-        <v>3.52</v>
+        <v>4.15</v>
       </c>
       <c r="T23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.2</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46076.64583333334</v>
+        <v>46076.625</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46076.66666666666</v>
+        <v>46076.64583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>4.16</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.55</v>
+        <v>6.49</v>
       </c>
       <c r="O26" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>1.66</v>
       </c>
       <c r="M27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N27" t="n">
         <v>4.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.34</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.75</v>
+        <v>1.34</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.29</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="N29" t="n">
-        <v>6.49</v>
+        <v>1.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>3.98</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.64</v>
+        <v>2.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46076.6875</v>
+        <v>46076.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="M32" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>5.09</v>
       </c>
       <c r="O32" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="M33" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="V33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>5.29</v>
       </c>
       <c r="M34" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>1.67</v>
       </c>
       <c r="O34" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.85</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE34" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="AF34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.29</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.67</v>
       </c>
-      <c r="O35" t="n">
-        <v>5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="N36" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.11</v>
+        <v>2.85</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="S36" t="n">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V36" t="n">
+        <v>11</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.48</v>
       </c>
-      <c r="V36" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC36" t="n">
-        <v>3.08</v>
+        <v>4.9</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,76 +4824,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="M37" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.83</v>
+        <v>1.55</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.65</v>
+        <v>2.11</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.75</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.79</v>
+        <v>3.08</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46076.69791666666</v>
+        <v>46076.6875</v>
       </c>
     </row>
     <row r="38">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>4.15</v>
+        <v>2.83</v>
       </c>
       <c r="O38" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
         <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="AD38" t="n">
         <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5021,27 +5021,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,76 +5062,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="M39" t="n">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="N39" t="n">
-        <v>5.66</v>
+        <v>4.15</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.45</v>
+        <v>4.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC39" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
         <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46076.70833333334</v>
+        <v>46076.69791666666</v>
       </c>
     </row>
     <row r="40">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>2.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.53</v>
+        <v>4.4</v>
       </c>
       <c r="R40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U40" t="n">
         <v>1.3</v>
       </c>
-      <c r="S40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V40" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>2.54</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>2.96</v>
+        <v>3.94</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>5.66</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.4</v>
+        <v>6.45</v>
       </c>
       <c r="R41" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
         <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,76 +5538,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>5.65</v>
+        <v>1.91</v>
       </c>
       <c r="O43" t="n">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.25</v>
+        <v>2.53</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AI43" s="3" t="n">
-        <v>46076.71875</v>
+        <v>46076.70833333334</v>
       </c>
     </row>
     <row r="44">
@@ -5735,27 +5735,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,76 +5776,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.98</v>
+        <v>3.86</v>
       </c>
       <c r="N45" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="O45" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U45" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V45" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA45" t="n">
         <v>2.09</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46076.75</v>
+        <v>46076.71875</v>
       </c>
     </row>
     <row r="46">
@@ -5854,27 +5854,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,76 +5895,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46076.79166666666</v>
+        <v>46076.75</v>
       </c>
     </row>
     <row r="47">
@@ -5973,27 +5973,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,76 +6014,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46076.85416666666</v>
+        <v>46076.79166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,76 +6133,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="M48" t="n">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46076.89583333334</v>
+        <v>46076.85416666666</v>
       </c>
     </row>
     <row r="49">
@@ -6321,6 +6321,125 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
+        <v>46076.89583333334</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
         <v>46076.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="M11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.1</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.41</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="N16" t="n">
-        <v>1.84</v>
+        <v>9.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.29</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>8.82</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.11</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4.04</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>3.29</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
         <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>6.3</v>
+        <v>4.04</v>
       </c>
       <c r="N18" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.82</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.31</v>
+        <v>2.81</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.1</v>
@@ -2959,34 +2959,34 @@
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.35</v>
+        <v>3.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>7.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB22" t="n">
         <v>3</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC22" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>1.99</v>
       </c>
       <c r="M23" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>3.66</v>
       </c>
       <c r="O23" t="n">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>13</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.15</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.22</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z23" t="n">
-        <v>6.25</v>
+        <v>4.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.91</v>
+        <v>2.64</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>11</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>6.34</v>
       </c>
       <c r="N26" t="n">
-        <v>6.49</v>
+        <v>1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="N28" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3.8</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="AA30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF30" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.7</v>
       </c>
       <c r="AG30" t="n">
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="O31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="M33" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S33" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AC33" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.29</v>
+        <v>1.91</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.67</v>
       </c>
-      <c r="O34" t="n">
-        <v>5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC34" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="P35" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="S35" t="n">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="T35" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.36</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.3</v>
+        <v>5.29</v>
       </c>
       <c r="M36" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="R36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.18</v>
       </c>
-      <c r="T36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V36" t="n">
-        <v>11</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AB36" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>5.66</v>
+        <v>1.91</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>4.05</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.45</v>
+        <v>2.53</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="N42" t="n">
-        <v>2.21</v>
+        <v>5.66</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>6.45</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="T42" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
         <v>7.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC42" t="n">
         <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.58</v>
       </c>
       <c r="AD42" t="n">
         <v>1.25</v>
       </c>
       <c r="AE42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF42" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF42" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF43" t="n">
         <v>1.91</v>
       </c>
-      <c r="O43" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V43" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="N44" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z44" t="n">
         <v>3.25</v>
       </c>
-      <c r="O44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V44" t="n">
-        <v>7</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.65</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.25</v>
+        <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S45" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH45" t="n">
-        <v>2.22</v>
+        <v>1.73</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1510,7 +1510,7 @@
         <v>3.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
         <v>2.62</v>
@@ -1519,13 +1519,13 @@
         <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1534,22 +1534,22 @@
         <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
         <v>2.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
         <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
         <v>1.91</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="M12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.1</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>5.59</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>5.94</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
         <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
@@ -2129,16 +2129,16 @@
         <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
@@ -2215,22 +2215,22 @@
         <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
@@ -2248,16 +2248,16 @@
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
         <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1.23</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>9.5</v>
+        <v>1.84</v>
       </c>
       <c r="O16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.7</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q16" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.23</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>10.31</v>
       </c>
       <c r="O17" t="n">
-        <v>3.29</v>
+        <v>1.65</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.11</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>4.03</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
@@ -2581,55 +2581,55 @@
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="T18" t="n">
         <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
         <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
         <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
@@ -2724,10 +2724,10 @@
         <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -2736,7 +2736,7 @@
         <v>2.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
         <v>1.7</v>
@@ -2745,7 +2745,7 @@
         <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
         <v>2.1</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.26</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.1</v>
@@ -2959,34 +2959,34 @@
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.66</v>
+        <v>4.43</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>6.15</v>
+        <v>1.59</v>
       </c>
       <c r="O25" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="P25" t="n">
         <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
         <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.7</v>
+        <v>1.13</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>11</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
-        <v>6.34</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.65</v>
+        <v>5.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
-        <v>4.9</v>
+        <v>3.98</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.05</v>
+        <v>2.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>6.15</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="R27" t="n">
         <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="U27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.67</v>
       </c>
-      <c r="V27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="AF27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.18</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>2.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>4.75</v>
+        <v>6.34</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.04</v>
+        <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>3.98</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.49</v>
+        <v>1.05</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.66</v>
       </c>
       <c r="M29" t="n">
-        <v>4.16</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
-        <v>1.55</v>
+        <v>4.72</v>
       </c>
       <c r="O29" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>4.72</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.57</v>
+        <v>3.43</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="N32" t="n">
-        <v>5.09</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>11</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.6</v>
       </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V32" t="n">
-        <v>8</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
         <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.3</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>5.09</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="P33" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>2.7</v>
@@ -4485,19 +4485,19 @@
         <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.06</v>
@@ -4506,13 +4506,13 @@
         <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
         <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
         <v>1.67</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>5.6</v>
       </c>
       <c r="M35" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>1.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>5.75</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.13</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.29</v>
+        <v>2.59</v>
       </c>
       <c r="M36" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O36" t="n">
         <v>3.4</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V36" t="n">
+        <v>12</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.67</v>
       </c>
-      <c r="O36" t="n">
-        <v>5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="Z36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE36" t="n">
         <v>2.38</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF36" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
         <v>1.55</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>2.11</v>
-      </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U37" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
         <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG37" t="n">
         <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
         <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,28 +5062,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="M39" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="O39" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
         <v>3</v>
@@ -5092,43 +5092,43 @@
         <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="U40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="N41" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA41" t="n">
         <v>1.91</v>
       </c>
-      <c r="O41" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T41" t="n">
+      <c r="AB41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH41" t="n">
         <v>2.4</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>5.66</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3.86</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.45</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF42" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG42" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="N43" t="n">
-        <v>2.21</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V43" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.44</v>
       </c>
-      <c r="S43" t="n">
+      <c r="Z43" t="n">
         <v>2.6</v>
       </c>
-      <c r="T43" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V43" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3</v>
-      </c>
       <c r="AA43" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.65</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.25</v>
+        <v>3.76</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V44" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG44" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>2.22</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z45" t="n">
         <v>3.25</v>
       </c>
-      <c r="O45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V45" t="n">
-        <v>7</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3</v>
-      </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AD45" t="n">
         <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="M11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.1</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.75</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.84</v>
+        <v>10.31</v>
       </c>
       <c r="O16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.6</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T16" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.11</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.23</v>
+        <v>4.03</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V17" t="n">
         <v>5.5</v>
       </c>
-      <c r="N17" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.03</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.26</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.99</v>
+        <v>1.09</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V21" t="n">
         <v>4</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>5.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.04</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="W26" t="n">
         <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.2</v>
       </c>
-      <c r="O28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="Z28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.65</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.05</v>
+        <v>1.91</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>4.75</v>
       </c>
       <c r="N29" t="n">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.13</v>
+        <v>11</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>6.34</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="P31" t="n">
         <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="V31" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.43</v>
+        <v>5.6</v>
       </c>
       <c r="M32" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.2</v>
       </c>
-      <c r="O32" t="n">
-        <v>4</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AF32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.25</v>
       </c>
-      <c r="V32" t="n">
-        <v>11</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>5.09</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T33" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>5.09</v>
       </c>
       <c r="O34" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U34" t="n">
         <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
         <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.6</v>
+        <v>2.59</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="N35" t="n">
-        <v>1.55</v>
+        <v>3.26</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.05</v>
+        <v>4.57</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="U35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.48</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.59</v>
+        <v>5.5</v>
       </c>
       <c r="M36" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.26</v>
+        <v>1.55</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="P36" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.57</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.25</v>
+        <v>3.58</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.5</v>
+        <v>3.43</v>
       </c>
       <c r="M37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T37" t="n">
         <v>3.4</v>
       </c>
-      <c r="N37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE37" t="n">
         <v>2.1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="AF37" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC37" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P38" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T38" t="n">
         <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W38" t="n">
         <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
         <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
         <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>5.66</v>
       </c>
       <c r="O40" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
         <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.45</v>
+        <v>6.45</v>
       </c>
       <c r="R40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.3</v>
       </c>
-      <c r="S40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="Z40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH40" t="n">
         <v>2.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
       <c r="M41" t="n">
-        <v>3.94</v>
+        <v>2.84</v>
       </c>
       <c r="N41" t="n">
-        <v>5.66</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P41" t="n">
         <v>2</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q41" t="n">
-        <v>6.45</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>10.25</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.45</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB42" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V42" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC42" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R43" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="T43" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>10.25</v>
+        <v>7.5</v>
       </c>
       <c r="W43" t="n">
         <v>1.05</v>
       </c>
       <c r="X43" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE43" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z44" t="n">
         <v>3.25</v>
       </c>
-      <c r="O44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V44" t="n">
-        <v>7</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF44" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S45" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH45" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>
@@ -6255,10 +6255,10 @@
         <v>1.67</v>
       </c>
       <c r="M49" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1379,13 +1379,13 @@
         <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="O8" t="n">
         <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
         <v>3.7</v>
@@ -1394,52 +1394,52 @@
         <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
         <v>2.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
         <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1501,25 +1501,25 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
         <v>3.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
         <v>8.1</v>
@@ -1534,31 +1534,31 @@
         <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
         <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46076.4375</v>
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.59</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>5.94</v>
+        <v>5.75</v>
       </c>
       <c r="P14" t="n">
         <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
       </c>
       <c r="U14" t="n">
         <v>1.39</v>
@@ -2129,31 +2129,31 @@
         <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA14" t="n">
         <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46076.54166666666</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="N16" t="n">
-        <v>10.31</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P16" t="n">
         <v>2.72</v>
@@ -2343,22 +2343,22 @@
         <v>7.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
         <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
@@ -2367,7 +2367,7 @@
         <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA16" t="n">
         <v>1.52</v>
@@ -2376,7 +2376,7 @@
         <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
         <v>1.57</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -2572,10 +2572,10 @@
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
@@ -2587,10 +2587,10 @@
         <v>3.12</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
         <v>5.75</v>
@@ -2605,28 +2605,28 @@
         <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
         <v>2.24</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.09</v>
+        <v>1.99</v>
       </c>
       <c r="M21" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.26</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.38</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE21" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.2</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>1.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q22" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V22" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>5.2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>6.34</v>
       </c>
       <c r="N25" t="n">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="O25" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="P25" t="n">
         <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.17</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>5.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="W26" t="n">
         <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>2.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="M27" t="n">
-        <v>4.8</v>
+        <v>3.52</v>
       </c>
       <c r="N27" t="n">
-        <v>6.15</v>
+        <v>4.72</v>
       </c>
       <c r="O27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.44</v>
       </c>
-      <c r="V28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AG28" t="n">
         <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="O29" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.04</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="V29" t="n">
-        <v>3.98</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>2.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>6.34</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="O31" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="P31" t="n">
         <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V31" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF31" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.6</v>
+        <v>2.09</v>
       </c>
       <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3.9</v>
       </c>
-      <c r="N32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O32" t="n">
-        <v>5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.05</v>
-      </c>
       <c r="R32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.33</v>
       </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V32" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
         <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.13</v>
+        <v>1.76</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>5.09</v>
       </c>
       <c r="O33" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U33" t="n">
         <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
         <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="M34" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>5.09</v>
+        <v>1.55</v>
       </c>
       <c r="O34" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.59</v>
+        <v>3.43</v>
       </c>
       <c r="M35" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="N35" t="n">
-        <v>3.26</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.4</v>
       </c>
-      <c r="P35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4.2</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE35" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA35" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="AF35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.43</v>
+        <v>2.59</v>
       </c>
       <c r="M37" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="N37" t="n">
-        <v>2.2</v>
+        <v>3.26</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.85</v>
+        <v>4.57</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="S37" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>5.66</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="P40" t="n">
         <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.45</v>
+        <v>2.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="U40" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="N42" t="n">
-        <v>1.91</v>
+        <v>5.66</v>
       </c>
       <c r="O42" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
         <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.45</v>
+        <v>6.45</v>
       </c>
       <c r="R42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y42" t="n">
         <v>1.3</v>
       </c>
-      <c r="S42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T42" t="n">
+      <c r="Z42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH42" t="n">
         <v>2.4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V42" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5553,16 +5553,16 @@
         <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="U43" t="n">
         <v>1.33</v>
@@ -5571,40 +5571,40 @@
         <v>7.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z43" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
         <v>3.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG43" t="n">
         <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5794,55 +5794,55 @@
         <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T45" t="n">
         <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V45" t="n">
         <v>7</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
         <v>1.23</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AA45" t="n">
         <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AD45" t="n">
         <v>1.23</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF45" t="n">
         <v>1.91</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1739,25 +1739,25 @@
         <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="P11" t="n">
         <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
         <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
         <v>8</v>
@@ -1766,13 +1766,13 @@
         <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
         <v>2.15</v>
@@ -1784,16 +1784,16 @@
         <v>3.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
         <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
         <v>1.4</v>
@@ -1852,25 +1852,25 @@
         <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="P12" t="n">
         <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
         <v>3.25</v>
@@ -1894,22 +1894,22 @@
         <v>2.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC12" t="n">
         <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
         <v>1.36</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="U17" t="n">
         <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O18" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
         <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
         <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
         <v>3.88</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -2700,10 +2700,10 @@
         <v>5.37</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
         <v>2.65</v>
@@ -2715,7 +2715,7 @@
         <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
@@ -2727,28 +2727,28 @@
         <v>4.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.77</v>
+        <v>3.03</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46076.60416666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.43</v>
+        <v>13.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="Q20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V20" t="n">
         <v>4</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>6.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2923,28 +2923,28 @@
         <v>1.99</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
         <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
         <v>1.48</v>
@@ -2953,40 +2953,40 @@
         <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD21" t="n">
         <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
         <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.26</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3277,19 +3277,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O24" t="n">
         <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
         <v>2.3</v>
@@ -3298,19 +3298,19 @@
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
@@ -3322,7 +3322,7 @@
         <v>5.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB24" t="n">
         <v>2.55</v>
@@ -3331,19 +3331,19 @@
         <v>2.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46076.64583333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
-        <v>6.34</v>
+        <v>3.52</v>
       </c>
       <c r="N25" t="n">
-        <v>1.2</v>
+        <v>4.72</v>
       </c>
       <c r="O25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.04</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="W26" t="n">
         <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>4.72</v>
+        <v>1.59</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>6.34</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="N29" t="n">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.5</v>
+        <v>5.04</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>3.98</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.59</v>
+        <v>6.15</v>
       </c>
       <c r="O31" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="P31" t="n">
         <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V31" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>1.12</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.13</v>
+        <v>2.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>5.09</v>
+        <v>1.55</v>
       </c>
       <c r="O33" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
         <v>1.55</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U34" t="n">
         <v>1.33</v>
       </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V34" t="n">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
         <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AG34" t="n">
         <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.43</v>
+        <v>2.59</v>
       </c>
       <c r="M35" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>3.26</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.85</v>
+        <v>4.57</v>
       </c>
       <c r="R35" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="S35" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.5</v>
+        <v>3.43</v>
       </c>
       <c r="M36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.4</v>
       </c>
-      <c r="N36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O36" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="U36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>11</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE36" t="n">
         <v>2.1</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="AF36" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC36" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.59</v>
+        <v>1.63</v>
       </c>
       <c r="M37" t="n">
-        <v>2.46</v>
+        <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>3.26</v>
+        <v>5.09</v>
       </c>
       <c r="O37" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="P37" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>4.33</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T38" t="n">
         <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
         <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF38" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF38" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="O39" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="P39" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC40" t="n">
         <v>3.8</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>2.84</v>
+        <v>3.94</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>5.66</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>6.45</v>
       </c>
       <c r="R41" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="T41" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="U41" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>10.25</v>
+        <v>7.6</v>
       </c>
       <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
         <v>1.05</v>
       </c>
-      <c r="X41" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>5.66</v>
+        <v>1.91</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
         <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.45</v>
+        <v>2.45</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
-        <v>3.86</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.97</v>
+        <v>4.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V43" t="n">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.09</v>
+        <v>2.58</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.11</v>
+        <v>2.49</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V44" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC44" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AF44" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z45" t="n">
         <v>3.25</v>
       </c>
-      <c r="O45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V45" t="n">
-        <v>7</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.17</v>
-      </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>
@@ -5895,52 +5895,52 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="M46" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="R46" t="n">
         <v>1.42</v>
       </c>
       <c r="S46" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V46" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
         <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AB46" t="n">
         <v>1.7</v>
@@ -5949,19 +5949,19 @@
         <v>3.8</v>
       </c>
       <c r="AD46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH46" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46076.75</v>
@@ -6133,61 +6133,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="M48" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="Q48" t="n">
         <v>3.86</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T48" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="U48" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
         <v>1.04</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z48" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB48" t="n">
         <v>1.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE48" t="n">
         <v>1.8</v>
@@ -6196,10 +6196,10 @@
         <v>1.91</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46076.85416666666</v>
@@ -6374,10 +6374,10 @@
         <v>1.67</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N50" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>1.84</v>
       </c>
       <c r="O16" t="n">
-        <v>1.64</v>
+        <v>4.07</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.03</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.84</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>1.64</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="U18" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.11</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>4.03</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.48</v>
+        <v>6.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>13.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.21</v>
+        <v>11.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.74</v>
+        <v>5.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.64</v>
+        <v>2.07</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>6.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="N23" t="n">
-        <v>4.43</v>
+        <v>3.59</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
         <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.66</v>
+        <v>8.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.52</v>
+        <v>5.75</v>
       </c>
       <c r="N25" t="n">
-        <v>4.72</v>
+        <v>1.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>5.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.59</v>
+        <v>2.62</v>
       </c>
       <c r="O27" t="n">
-        <v>4.92</v>
+        <v>2.73</v>
       </c>
       <c r="P27" t="n">
         <v>2.59</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.06</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.27</v>
+        <v>2.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>11</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>6.34</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="O28" t="n">
-        <v>8.5</v>
+        <v>2.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.65</v>
+        <v>5.43</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.05</v>
+        <v>2.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.46</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="V29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.18</v>
       </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V29" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>3.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.4</v>
+        <v>5.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.8</v>
+        <v>5.64</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,43 +4110,43 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>6.15</v>
+        <v>1.59</v>
       </c>
       <c r="O31" t="n">
-        <v>1.85</v>
+        <v>4.92</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U31" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V31" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
         <v>1.12</v>
@@ -4155,28 +4155,28 @@
         <v>4.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.7</v>
+        <v>1.12</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.09</v>
+        <v>3.43</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="S32" t="n">
-        <v>2.72</v>
+        <v>2.33</v>
       </c>
       <c r="T32" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE32" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
         <v>1.55</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.5</v>
+        <v>2.59</v>
       </c>
       <c r="M34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.4</v>
       </c>
-      <c r="N34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O34" t="n">
-        <v>5.25</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V34" t="n">
+        <v>12</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.1</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.18</v>
+        <v>3.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.58</v>
+        <v>6.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.59</v>
+        <v>1.63</v>
       </c>
       <c r="M35" t="n">
-        <v>2.46</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>3.26</v>
+        <v>5.09</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="U35" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AC35" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.43</v>
+        <v>2.09</v>
       </c>
       <c r="M36" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="S36" t="n">
-        <v>2.33</v>
+        <v>2.72</v>
       </c>
       <c r="T36" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
         <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N37" t="n">
-        <v>5.09</v>
+        <v>1.55</v>
       </c>
       <c r="O37" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="O38" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="P38" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="R38" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.95</v>
       </c>
-      <c r="O39" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="AA39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.33</v>
       </c>
-      <c r="V39" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>5.66</v>
       </c>
       <c r="O40" t="n">
-        <v>3.86</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.97</v>
+        <v>6.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="U40" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V40" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W40" t="n">
         <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AD40" t="n">
         <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.57</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>5.66</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>3.86</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.45</v>
+        <v>2.97</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S41" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
-        <v>2.94</v>
+        <v>3.14</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AD41" t="n">
         <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T42" t="n">
         <v>3.5</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>5.5</v>
+        <v>10.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.18</v>
+        <v>3.66</v>
       </c>
       <c r="M43" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="R43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.61</v>
       </c>
-      <c r="S43" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="AF43" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.28</v>
       </c>
-      <c r="V43" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V44" t="n">
-        <v>7</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG44" t="n">
         <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V45" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC45" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AF45" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.63</v>
+        <v>2.54</v>
       </c>
       <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>2.54</v>
+        <v>3.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.89</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.02</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2218,10 +2218,10 @@
         <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R15" t="n">
         <v>1.38</v>
@@ -2230,49 +2230,49 @@
         <v>2.67</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
         <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46076.57291666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.07</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="U16" t="n">
         <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>2.24</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>2.08</v>
+        <v>4.07</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
         <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="N22" t="n">
-        <v>4.43</v>
+        <v>3.59</v>
       </c>
       <c r="O22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
         <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>8.5</v>
+        <v>1.36</v>
       </c>
       <c r="M25" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.29</v>
+        <v>7.5</v>
       </c>
       <c r="O25" t="n">
-        <v>7.85</v>
+        <v>1.86</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.61</v>
+        <v>5.81</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
         <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.81</v>
+        <v>4.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>3.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
         <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.73</v>
+        <v>2.24</v>
       </c>
       <c r="P27" t="n">
-        <v>2.59</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.19</v>
+        <v>5.43</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.83</v>
+        <v>3.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.59</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.06</v>
+        <v>3.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.58</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="N28" t="n">
-        <v>5.6</v>
+        <v>1.29</v>
       </c>
       <c r="O28" t="n">
-        <v>2.24</v>
+        <v>7.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.43</v>
+        <v>1.61</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>2.74</v>
+        <v>2.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.01</v>
+        <v>1.03</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O29" t="n">
-        <v>2.18</v>
+        <v>4.92</v>
       </c>
       <c r="P29" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q29" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.23</v>
+        <v>1.12</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="O30" t="n">
-        <v>1.95</v>
+        <v>2.73</v>
       </c>
       <c r="P30" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.04</v>
+        <v>3.19</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="W30" t="n">
         <v>1.16</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.64</v>
+        <v>5.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V31" t="n">
         <v>4.2</v>
       </c>
-      <c r="N31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O31" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
         <v>1.12</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.75</v>
+        <v>5.64</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AF31" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.27</v>
       </c>
       <c r="AG31" t="n">
         <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.12</v>
+        <v>2.43</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4229,43 +4229,43 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="R32" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S32" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="T32" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U32" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V32" t="n">
         <v>11</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y32" t="n">
         <v>1.5</v>
@@ -4283,19 +4283,19 @@
         <v>4.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.5</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>1.55</v>
+        <v>5.09</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>2.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
         <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>2.07</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.59</v>
+        <v>2.09</v>
       </c>
       <c r="M34" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="T34" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="U34" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC34" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>5.09</v>
+        <v>1.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N36" t="n">
         <v>3.25</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O36" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>4.57</v>
       </c>
       <c r="R36" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="S36" t="n">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="T36" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="U36" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="V36" t="n">
+        <v>11</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC36" t="n">
         <v>6.5</v>
       </c>
-      <c r="W36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X36" t="n">
+      <c r="AD36" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE36" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,70 +4824,70 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>7.15</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.09</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V37" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
         <v>1.06</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2.95</v>
       </c>
-      <c r="O38" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="AA38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.33</v>
       </c>
-      <c r="V38" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="O39" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="P39" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46076.69791666666</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.94</v>
+        <v>2.84</v>
       </c>
       <c r="N40" t="n">
-        <v>5.66</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P40" t="n">
         <v>2</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q40" t="n">
-        <v>6.45</v>
+        <v>4.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="S40" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="T40" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U40" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V40" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
         <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC40" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>3.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.45</v>
       </c>
-      <c r="O41" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.97</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC41" t="n">
         <v>2.75</v>
       </c>
-      <c r="T41" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AG41" t="n">
         <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="R42" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="S42" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="T42" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="U42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.28</v>
       </c>
-      <c r="V42" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.66</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>5.66</v>
       </c>
       <c r="O43" t="n">
-        <v>4.05</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
         <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.45</v>
+        <v>6.45</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
-        <v>3.36</v>
+        <v>2.77</v>
       </c>
       <c r="T43" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="U43" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="M11" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>2.54</v>
+        <v>3.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.89</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.63</v>
+        <v>2.54</v>
       </c>
       <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.61</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.83</v>
+        <v>4.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.24</v>
+        <v>4.03</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.07</v>
+        <v>2.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="U17" t="n">
         <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>2.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="M18" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>1.84</v>
       </c>
       <c r="O18" t="n">
-        <v>1.64</v>
+        <v>4.07</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.03</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,43 +3396,43 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.36</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>7.5</v>
+        <v>1.59</v>
       </c>
       <c r="O25" t="n">
-        <v>1.86</v>
+        <v>4.92</v>
       </c>
       <c r="P25" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.81</v>
+        <v>2.06</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
         <v>1.12</v>
@@ -3441,28 +3441,28 @@
         <v>4.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.27</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.84</v>
+        <v>5.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.22</v>
+        <v>3.84</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="V26" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.88</v>
+        <v>5.64</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.58</v>
+        <v>8.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="N27" t="n">
-        <v>5.6</v>
+        <v>1.29</v>
       </c>
       <c r="O27" t="n">
-        <v>2.24</v>
+        <v>7.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.43</v>
+        <v>1.61</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="T27" t="n">
-        <v>2.74</v>
+        <v>2.26</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.01</v>
+        <v>1.03</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.29</v>
+        <v>2.62</v>
       </c>
       <c r="O28" t="n">
-        <v>7.85</v>
+        <v>2.73</v>
       </c>
       <c r="P28" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.61</v>
+        <v>3.19</v>
       </c>
       <c r="R28" t="n">
         <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="T28" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.45</v>
+        <v>5.83</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.01</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>2.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,43 +3872,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>1.59</v>
+        <v>7.5</v>
       </c>
       <c r="O29" t="n">
-        <v>4.92</v>
+        <v>1.86</v>
       </c>
       <c r="P29" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.06</v>
+        <v>5.81</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>1.12</v>
@@ -3917,28 +3917,28 @@
         <v>4.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.12</v>
+        <v>2.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="P30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.59</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.04</v>
+        <v>5.43</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3.84</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.74</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.64</v>
+        <v>3.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.74</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="M32" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="R32" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>11</v>
+        <v>7.1</v>
       </c>
       <c r="W32" t="n">
         <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46076.6875</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>5.09</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T33" t="n">
         <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.09</v>
+        <v>3.35</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O34" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>3.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="T34" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="N35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V35" t="n">
+        <v>11</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.55</v>
       </c>
-      <c r="O35" t="n">
-        <v>5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V35" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG35" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.06</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>7.15</v>
       </c>
       <c r="P36" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.57</v>
+        <v>2.08</v>
       </c>
       <c r="R36" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="T36" t="n">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="U36" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="V36" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.06</v>
+        <v>2.83</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.2</v>
+        <v>1.63</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>1.6</v>
+        <v>5.09</v>
       </c>
       <c r="O37" t="n">
-        <v>7.15</v>
+        <v>2.22</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S37" t="n">
         <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
         <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD37" t="n">
         <v>1.21</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.06</v>
+        <v>2.07</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.66</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S41" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="U41" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.05</v>
+        <v>3.09</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AG41" t="n">
         <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>5.66</v>
       </c>
       <c r="O42" t="n">
-        <v>3.86</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.97</v>
+        <v>6.45</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T42" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W42" t="n">
         <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AD42" t="n">
         <v>1.25</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.57</v>
+        <v>3.66</v>
       </c>
       <c r="M43" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>5.66</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>4.05</v>
       </c>
       <c r="P43" t="n">
         <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.45</v>
+        <v>2.45</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>2.77</v>
+        <v>3.36</v>
       </c>
       <c r="T43" t="n">
-        <v>2.94</v>
+        <v>2.52</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="V43" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.04</v>
+        <v>3.76</v>
       </c>
       <c r="R44" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V44" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC44" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AF44" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG44" t="n">
         <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.32</v>
+        <v>1.72</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46076.71875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V45" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V45" t="n">
-        <v>7</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG45" t="n">
         <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46076.71875</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.63</v>
+        <v>2.54</v>
       </c>
       <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>2.54</v>
+        <v>3.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.89</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.02</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>1.84</v>
       </c>
       <c r="O16" t="n">
-        <v>1.64</v>
+        <v>4.07</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.03</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.84</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
-        <v>4.07</v>
+        <v>1.64</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>7.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="U18" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>4.03</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="M21" t="n">
-        <v>6.1</v>
+        <v>3.48</v>
       </c>
       <c r="N21" t="n">
-        <v>13.2</v>
+        <v>3.59</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>11.7</v>
+        <v>4.21</v>
       </c>
       <c r="R21" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.55</v>
+        <v>3.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.43</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="M22" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.59</v>
+        <v>4.43</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="T22" t="n">
         <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="O25" t="n">
-        <v>4.92</v>
+        <v>7.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="T25" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>1.59</v>
       </c>
       <c r="O26" t="n">
-        <v>1.95</v>
+        <v>4.92</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.04</v>
+        <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="U26" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.64</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AG26" t="n">
         <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.43</v>
+        <v>1.12</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8.5</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.29</v>
+        <v>7.5</v>
       </c>
       <c r="O27" t="n">
-        <v>7.85</v>
+        <v>1.86</v>
       </c>
       <c r="P27" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.61</v>
+        <v>5.81</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
         <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="P28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.59</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N29" t="n">
         <v>5</v>
       </c>
-      <c r="N29" t="n">
-        <v>7.5</v>
-      </c>
       <c r="O29" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="P29" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.81</v>
+        <v>5.04</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
         <v>1.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.75</v>
+        <v>5.64</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.84</v>
+        <v>5.43</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="U30" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>5.6</v>
+        <v>2.62</v>
       </c>
       <c r="O31" t="n">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>2.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.43</v>
+        <v>3.19</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="T31" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH31" t="n">
-        <v>2.01</v>
+        <v>1.58</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46076.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>5.09</v>
       </c>
       <c r="O33" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
         <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46076.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="M35" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="T35" t="n">
-        <v>4.33</v>
+        <v>3.04</v>
       </c>
       <c r="U35" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46076.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="N37" t="n">
-        <v>5.09</v>
+        <v>3.25</v>
       </c>
       <c r="O37" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="R37" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="U37" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="V37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W37" t="n">
         <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.07</v>
+        <v>1.45</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46076.6875</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>2.84</v>
+        <v>3.94</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>5.66</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.4</v>
+        <v>6.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="U40" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V40" t="n">
-        <v>10.2</v>
+        <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
         <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>3.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.45</v>
       </c>
-      <c r="O41" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.97</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC41" t="n">
         <v>2.75</v>
       </c>
-      <c r="T41" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AG41" t="n">
         <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="M42" t="n">
-        <v>3.94</v>
+        <v>2.84</v>
       </c>
       <c r="N42" t="n">
-        <v>5.66</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P42" t="n">
         <v>2</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q42" t="n">
-        <v>6.45</v>
+        <v>4.4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="S42" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="T42" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
         <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46076.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.66</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="U43" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.05</v>
+        <v>3.09</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AG43" t="n">
         <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46076.70833333334</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>

--- a/jogos_2026-02-23.xlsx
+++ b/jogos_2026-02-23.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46076.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46076.3125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46076.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="M11" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>2.54</v>
+        <v>3.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.89</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46076.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.63</v>
+        <v>2.54</v>
       </c>
       <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46076.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.84</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>4.07</v>
+        <v>1.64</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>7.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>4.03</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>2.08</v>
+        <v>4.07</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
         <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="T18" t="n">
-        <v>2.23</v>
+        <v>2.61</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.7</v>
+        <v>3.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.03</v>
+        <v>2.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46076.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>13.2</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.41</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.7</v>
-      </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>6.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.55</v>
+        <v>3.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.43</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46076.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46076.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4.43</v>
+        <v>13.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="Q22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V22" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.45</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH22" t="n">
-        <v>2.09</v>
+        <v>6.43</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46076.625</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46076.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>8.5</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>7.85</v>
+        <v>1.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.61</v>
+        <v>5.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.45</v>
+        <v>5.64</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.03</v>
+        <v>2.43</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.59</v>
+        <v>2.62</v>
       </c>
       <c r="O26" t="n">
-        <v>4.92</v>
+        <v>2.73</v>
       </c>
       <c r="P26" t="n">
         <v>2.59</v>
       </c>
       <c r="Q26" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.06</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.27</v>
+        <v>2.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.81</v>
+        <v>4.84</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.75</v>
+        <v>3.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF27" t="n">
         <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.84</v>
+        <v>5.43</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46076.66666666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>4.6</v>
       </c>
       <c 